--- a/data/trans_orig/P26-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P26-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2007</t>
+          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2007 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>208838</t>
+          <t>209356</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>252249</t>
+          <t>250918</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>195014</t>
+          <t>192109</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>236612</t>
+          <t>235153</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>415176</t>
+          <t>416343</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>476279</t>
+          <t>472657</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>50,88%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>221150</t>
+          <t>222481</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>264561</t>
+          <t>264043</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>218968</t>
+          <t>220427</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>260566</t>
+          <t>263471</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>452700</t>
+          <t>456322</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>513803</t>
+          <t>512636</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,18%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>209874</t>
+          <t>210715</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>258861</t>
+          <t>260101</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>220246</t>
+          <t>219395</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>269395</t>
+          <t>269862</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>441734</t>
+          <t>444327</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>514011</t>
+          <t>514259</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,77%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>437364</t>
+          <t>436124</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>486351</t>
+          <t>485510</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327418</t>
+          <t>326951</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>376567</t>
+          <t>377418</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>779027</t>
+          <t>778779</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>851304</t>
+          <t>848711</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,64%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>120159</t>
+          <t>120356</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>161292</t>
+          <t>160282</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>240496</t>
+          <t>237095</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>289678</t>
+          <t>288988</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>373373</t>
+          <t>369585</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>438726</t>
+          <t>439505</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,59%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>442450</t>
+          <t>443460</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>483583</t>
+          <t>483386</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>377144</t>
+          <t>377834</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>426326</t>
+          <t>429727</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>831838</t>
+          <t>831059</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>897191</t>
+          <t>900979</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,91%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>126601</t>
+          <t>128196</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>169746</t>
+          <t>170272</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>186821</t>
+          <t>185538</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>229909</t>
+          <t>229145</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>321759</t>
+          <t>327279</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>382597</t>
+          <t>388208</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,86%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>318272</t>
+          <t>317746</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>361417</t>
+          <t>359822</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>255925</t>
+          <t>256689</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>299013</t>
+          <t>300296</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>591255</t>
+          <t>585644</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>652093</t>
+          <t>646573</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>66,39%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63820</t>
+          <t>64338</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96419</t>
+          <t>96555</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>103033</t>
+          <t>104958</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>140074</t>
+          <t>140793</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>179684</t>
+          <t>178530</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>224422</t>
+          <t>225174</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>264911</t>
+          <t>264775</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>297510</t>
+          <t>296992</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>233410</t>
+          <t>232691</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>270451</t>
+          <t>268526</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>510391</t>
+          <t>509639</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>555129</t>
+          <t>556283</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,7%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17548</t>
+          <t>17410</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36473</t>
+          <t>37902</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41651</t>
+          <t>42099</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65404</t>
+          <t>66624</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>63070</t>
+          <t>64220</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>97078</t>
+          <t>94100</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225028</t>
+          <t>223599</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>243953</t>
+          <t>244091</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>212349</t>
+          <t>211129</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>236102</t>
+          <t>235654</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>442176</t>
+          <t>445154</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>476184</t>
+          <t>475034</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,09%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11283</t>
+          <t>11028</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27674</t>
+          <t>27926</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29661</t>
+          <t>29461</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55002</t>
+          <t>55207</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>45793</t>
+          <t>45211</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>76328</t>
+          <t>76053</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,84%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>139979</t>
+          <t>139727</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>156370</t>
+          <t>156625</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>181099</t>
+          <t>180894</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>206440</t>
+          <t>206640</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>327426</t>
+          <t>327701</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>357961</t>
+          <t>358543</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,8%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>819766</t>
+          <t>824973</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>919521</t>
+          <t>926295</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1092109</t>
+          <t>1093745</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1200621</t>
+          <t>1202815</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1943595</t>
+          <t>1943490</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2094258</t>
+          <t>2096193</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2132345</t>
+          <t>2125571</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2232100</t>
+          <t>2226893</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1891766</t>
+          <t>1889572</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2000278</t>
+          <t>1998642</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4049995</t>
+          <t>4048060</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4200658</t>
+          <t>4200763</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2012</t>
+          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2012 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>215319</t>
+          <t>211898</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>256160</t>
+          <t>253604</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>199535</t>
+          <t>197971</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>239696</t>
+          <t>239083</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>424155</t>
+          <t>425507</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>481277</t>
+          <t>480354</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,28%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>190981</t>
+          <t>193537</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>231822</t>
+          <t>235243</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>182104</t>
+          <t>182717</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>222265</t>
+          <t>223829</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>387663</t>
+          <t>388586</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>444785</t>
+          <t>443433</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,03%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>229325</t>
+          <t>229151</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>281640</t>
+          <t>280103</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>214944</t>
+          <t>215211</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>264660</t>
+          <t>266143</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>459529</t>
+          <t>460555</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>529454</t>
+          <t>531318</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,48%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>374006</t>
+          <t>375543</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>426321</t>
+          <t>426495</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>330493</t>
+          <t>329010</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>380209</t>
+          <t>379942</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>721345</t>
+          <t>719481</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>791270</t>
+          <t>790244</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,18%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>184883</t>
+          <t>183814</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>233865</t>
+          <t>232680</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>252483</t>
+          <t>251390</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>308431</t>
+          <t>303296</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>449189</t>
+          <t>445887</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>521716</t>
+          <t>521232</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,2%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>429627</t>
+          <t>430812</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>478609</t>
+          <t>479678</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>392649</t>
+          <t>397784</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>448597</t>
+          <t>449690</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>842856</t>
+          <t>843340</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>915383</t>
+          <t>918685</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>67,32%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>173255</t>
+          <t>172874</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>221708</t>
+          <t>220932</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>255863</t>
+          <t>252820</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>307007</t>
+          <t>306779</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>438501</t>
+          <t>438990</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>513332</t>
+          <t>511016</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,45%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>361162</t>
+          <t>361938</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>409615</t>
+          <t>409996</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>286106</t>
+          <t>286334</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>337250</t>
+          <t>340293</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>662651</t>
+          <t>664967</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>737482</t>
+          <t>736993</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,67%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92563</t>
+          <t>91921</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>128780</t>
+          <t>131394</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>137456</t>
+          <t>135522</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>175377</t>
+          <t>177042</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>238853</t>
+          <t>238603</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>295213</t>
+          <t>294971</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,11%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>284635</t>
+          <t>282021</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>320852</t>
+          <t>321494</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>251237</t>
+          <t>249572</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>289158</t>
+          <t>291092</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>544816</t>
+          <t>545058</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>601176</t>
+          <t>601426</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,6%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40559</t>
+          <t>39317</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68968</t>
+          <t>65541</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57368</t>
+          <t>58703</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88158</t>
+          <t>87670</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>104762</t>
+          <t>104704</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>147865</t>
+          <t>146375</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>221422</t>
+          <t>224849</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>249831</t>
+          <t>251073</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>218641</t>
+          <t>219129</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>249431</t>
+          <t>248096</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>449325</t>
+          <t>450815</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>492428</t>
+          <t>492486</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,47%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16080</t>
+          <t>15678</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36195</t>
+          <t>37592</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43666</t>
+          <t>43975</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71284</t>
+          <t>72800</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64372</t>
+          <t>65580</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>101966</t>
+          <t>100722</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>191327</t>
+          <t>189930</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>211442</t>
+          <t>211844</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>246950</t>
+          <t>245434</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>274568</t>
+          <t>274259</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>443791</t>
+          <t>445035</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>481385</t>
+          <t>480177</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>87,98%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1030129</t>
+          <t>1027083</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1135805</t>
+          <t>1135492</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1249274</t>
+          <t>1240770</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1358923</t>
+          <t>1360887</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2301312</t>
+          <t>2297091</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2464960</t>
+          <t>2459735</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,03%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2144672</t>
+          <t>2144985</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2250348</t>
+          <t>2253394</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2003869</t>
+          <t>2001905</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2113518</t>
+          <t>2122022</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4178310</t>
+          <t>4183535</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4341958</t>
+          <t>4346179</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,42%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2016</t>
+          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2016 (tasa de respuesta: 99,58%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>143148</t>
+          <t>144898</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>183551</t>
+          <t>185713</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>122118</t>
+          <t>121785</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>159327</t>
+          <t>157700</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>274021</t>
+          <t>278743</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>331180</t>
+          <t>330971</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,74%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>227740</t>
+          <t>225578</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>268143</t>
+          <t>266393</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>222273</t>
+          <t>223900</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259482</t>
+          <t>259815</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>461711</t>
+          <t>461920</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>518870</t>
+          <t>514148</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>64,84%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>151224</t>
+          <t>150638</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>193690</t>
+          <t>196024</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>170498</t>
+          <t>170534</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>214608</t>
+          <t>213086</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>334192</t>
+          <t>330252</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>392363</t>
+          <t>391399</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,68%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>363009</t>
+          <t>360675</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>405475</t>
+          <t>406061</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>325704</t>
+          <t>327226</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369814</t>
+          <t>369778</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>704648</t>
+          <t>705612</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>762819</t>
+          <t>766759</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,9%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>131243</t>
+          <t>133001</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>175956</t>
+          <t>175293</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>152957</t>
+          <t>153985</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>195293</t>
+          <t>199460</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>299091</t>
+          <t>298745</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>359903</t>
+          <t>362669</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,77%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>441236</t>
+          <t>441899</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>485949</t>
+          <t>484191</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>447913</t>
+          <t>443746</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>490249</t>
+          <t>489221</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>900495</t>
+          <t>897729</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>961307</t>
+          <t>961653</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,3%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>126077</t>
+          <t>127560</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>168935</t>
+          <t>171803</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>159568</t>
+          <t>160048</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>207474</t>
+          <t>207138</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>297255</t>
+          <t>299602</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>362623</t>
+          <t>364210</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,63%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>429929</t>
+          <t>427061</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>472787</t>
+          <t>471304</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>422656</t>
+          <t>422992</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>470562</t>
+          <t>470082</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>866371</t>
+          <t>864784</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>931739</t>
+          <t>929392</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,62%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>87666</t>
+          <t>86244</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>123258</t>
+          <t>123215</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>95832</t>
+          <t>96568</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>133044</t>
+          <t>134466</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>192293</t>
+          <t>191475</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>247987</t>
+          <t>244685</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,29%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>319008</t>
+          <t>319051</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>354600</t>
+          <t>356022</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>321224</t>
+          <t>319802</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>358436</t>
+          <t>357700</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>648547</t>
+          <t>651849</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>704241</t>
+          <t>705059</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,64%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28108</t>
+          <t>27576</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50919</t>
+          <t>51741</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32706</t>
+          <t>32833</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57766</t>
+          <t>58658</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>66266</t>
+          <t>66164</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>100944</t>
+          <t>101210</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254444</t>
+          <t>253622</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>277255</t>
+          <t>277787</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>263957</t>
+          <t>263065</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>289017</t>
+          <t>288890</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>526142</t>
+          <t>525876</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>560820</t>
+          <t>560922</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,45%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>9649</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22261</t>
+          <t>22055</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21716</t>
+          <t>21562</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47670</t>
+          <t>46321</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36477</t>
+          <t>34626</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64816</t>
+          <t>62721</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>197006</t>
+          <t>197212</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>210281</t>
+          <t>209618</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>264427</t>
+          <t>265776</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>290381</t>
+          <t>290535</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>466549</t>
+          <t>468644</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>494888</t>
+          <t>496739</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,48%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>744248</t>
+          <t>747042</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>846071</t>
+          <t>847666</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>824932</t>
+          <t>822229</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>925972</t>
+          <t>926247</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1599733</t>
+          <t>1603052</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1747684</t>
+          <t>1748846</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,18%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2304871</t>
+          <t>2303276</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2406694</t>
+          <t>2403900</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2357365</t>
+          <t>2357090</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2458405</t>
+          <t>2461108</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4686595</t>
+          <t>4685433</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4834546</t>
+          <t>4831227</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,09%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2023</t>
+          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52202</t>
+          <t>50453</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>107512</t>
+          <t>109003</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47336</t>
+          <t>47859</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86614</t>
+          <t>88189</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>112693</t>
+          <t>113458</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>180185</t>
+          <t>182169</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>283229</t>
+          <t>281738</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>338539</t>
+          <t>340288</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>215854</t>
+          <t>214279</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>255132</t>
+          <t>254609</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>513023</t>
+          <t>511039</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>580515</t>
+          <t>579750</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,63%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46921</t>
+          <t>46712</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87937</t>
+          <t>87200</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51693</t>
+          <t>49739</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107673</t>
+          <t>105934</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108724</t>
+          <t>112182</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>176894</t>
+          <t>180999</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>300303</t>
+          <t>301040</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>341319</t>
+          <t>341528</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>389608</t>
+          <t>391347</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>445588</t>
+          <t>447542</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>708628</t>
+          <t>704523</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>776798</t>
+          <t>773340</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,33%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33594</t>
+          <t>32749</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60647</t>
+          <t>60457</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61043</t>
+          <t>60900</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88284</t>
+          <t>86698</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102191</t>
+          <t>100145</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>137852</t>
+          <t>137776</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>438112</t>
+          <t>438302</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>465165</t>
+          <t>466010</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>435929</t>
+          <t>437515</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>463170</t>
+          <t>463313</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>885120</t>
+          <t>885196</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>920781</t>
+          <t>922827</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,21%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84652</t>
+          <t>83337</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>589955</t>
+          <t>587150</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79460</t>
+          <t>79294</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111529</t>
+          <t>110513</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>182990</t>
+          <t>180574</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>848508</t>
+          <t>895151</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>59,43%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>223904</t>
+          <t>226709</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>729207</t>
+          <t>730522</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>580719</t>
+          <t>581735</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>612788</t>
+          <t>612954</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>657599</t>
+          <t>610956</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1323117</t>
+          <t>1325533</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,01%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51658</t>
+          <t>51878</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>80850</t>
+          <t>79525</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54207</t>
+          <t>54117</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75893</t>
+          <t>77173</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>112309</t>
+          <t>113375</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>148007</t>
+          <t>148745</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>430112</t>
+          <t>431437</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>459304</t>
+          <t>459084</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>416379</t>
+          <t>415099</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>438065</t>
+          <t>438155</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>855227</t>
+          <t>854489</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>890925</t>
+          <t>889859</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,7%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14660</t>
+          <t>15675</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29278</t>
+          <t>30556</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11276</t>
+          <t>11694</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57850</t>
+          <t>57812</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27123</t>
+          <t>27679</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75865</t>
+          <t>76532</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>297672</t>
+          <t>296394</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>312290</t>
+          <t>311275</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>482687</t>
+          <t>482725</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>529261</t>
+          <t>528843</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>791623</t>
+          <t>790956</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>840365</t>
+          <t>839809</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7468</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13630</t>
+          <t>13271</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25527</t>
+          <t>26125</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15961</t>
+          <t>15663</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29558</t>
+          <t>29385</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>233002</t>
+          <t>233007</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>239440</t>
+          <t>239261</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>290251</t>
+          <t>289653</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>302148</t>
+          <t>302507</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>526690</t>
+          <t>526863</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>540287</t>
+          <t>540585</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>362671</t>
+          <t>354939</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1220357</t>
+          <t>1164886</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>348927</t>
+          <t>344940</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>481007</t>
+          <t>485998</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>781055</t>
+          <t>776418</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1741870</t>
+          <t>1717584</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1949624</t>
+          <t>2005095</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2807310</t>
+          <t>2815042</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2883790</t>
+          <t>2878799</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3015870</t>
+          <t>3019857</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4792908</t>
+          <t>4817194</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5753723</t>
+          <t>5758360</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P26-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P26-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>209356</t>
+          <t>209118</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>250918</t>
+          <t>251434</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>192109</t>
+          <t>194246</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>235153</t>
+          <t>232897</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>416343</t>
+          <t>416028</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>472657</t>
+          <t>474009</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>51,02%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>222481</t>
+          <t>221965</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>264043</t>
+          <t>264281</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>220427</t>
+          <t>222683</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>263471</t>
+          <t>261334</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>456322</t>
+          <t>454970</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>512636</t>
+          <t>512951</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,22%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>210715</t>
+          <t>208904</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>260101</t>
+          <t>259222</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>219395</t>
+          <t>219524</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>269862</t>
+          <t>268505</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>444327</t>
+          <t>444664</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>514259</t>
+          <t>515060</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>436124</t>
+          <t>437003</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>485510</t>
+          <t>487321</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>326951</t>
+          <t>328308</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>377418</t>
+          <t>377289</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>778779</t>
+          <t>777978</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>848711</t>
+          <t>848374</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,61%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>120356</t>
+          <t>118980</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>160282</t>
+          <t>162583</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>237095</t>
+          <t>240366</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>288988</t>
+          <t>289654</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>369585</t>
+          <t>372564</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>439505</t>
+          <t>437757</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,45%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>443460</t>
+          <t>441159</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>483386</t>
+          <t>484762</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>377834</t>
+          <t>377168</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>429727</t>
+          <t>426456</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>831059</t>
+          <t>832807</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>900979</t>
+          <t>898000</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,68%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>128196</t>
+          <t>126055</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>170272</t>
+          <t>169747</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>185538</t>
+          <t>185715</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>229145</t>
+          <t>228969</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>327279</t>
+          <t>324353</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>388208</t>
+          <t>386946</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,73%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>317746</t>
+          <t>318271</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>359822</t>
+          <t>361963</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>256689</t>
+          <t>256865</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>300296</t>
+          <t>300119</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>585644</t>
+          <t>586906</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>646573</t>
+          <t>649499</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,69%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64338</t>
+          <t>64426</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96555</t>
+          <t>95157</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>104958</t>
+          <t>105272</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>140793</t>
+          <t>139976</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>178530</t>
+          <t>177112</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>225174</t>
+          <t>226877</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>264775</t>
+          <t>266173</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>296992</t>
+          <t>296904</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>232691</t>
+          <t>233508</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>268526</t>
+          <t>268212</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>509639</t>
+          <t>507936</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>556283</t>
+          <t>557701</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>75,9%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17410</t>
+          <t>16587</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37902</t>
+          <t>35627</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42099</t>
+          <t>42058</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>66624</t>
+          <t>66368</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64220</t>
+          <t>64115</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>94100</t>
+          <t>95043</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>223599</t>
+          <t>225874</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>244091</t>
+          <t>244914</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>211129</t>
+          <t>211385</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>235654</t>
+          <t>235695</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>445154</t>
+          <t>444211</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>475034</t>
+          <t>475139</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,11%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11028</t>
+          <t>11975</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27926</t>
+          <t>29109</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29461</t>
+          <t>29250</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55207</t>
+          <t>54021</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>45211</t>
+          <t>44467</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>76053</t>
+          <t>74889</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>139727</t>
+          <t>138544</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>156625</t>
+          <t>155678</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>180894</t>
+          <t>182080</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>206640</t>
+          <t>206851</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>327701</t>
+          <t>328865</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>358543</t>
+          <t>359287</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,99%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>824973</t>
+          <t>818869</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>926295</t>
+          <t>923660</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1093745</t>
+          <t>1097897</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1202815</t>
+          <t>1201372</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1943490</t>
+          <t>1949927</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2096193</t>
+          <t>2091256</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,04%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2125571</t>
+          <t>2128206</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2226893</t>
+          <t>2232997</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1889572</t>
+          <t>1891015</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1998642</t>
+          <t>1994490</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4048060</t>
+          <t>4052997</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4200763</t>
+          <t>4194326</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>211898</t>
+          <t>211256</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>253604</t>
+          <t>255152</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>197971</t>
+          <t>198569</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>239083</t>
+          <t>238588</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>425507</t>
+          <t>426078</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>480354</t>
+          <t>485170</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,83%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>193537</t>
+          <t>191989</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>235243</t>
+          <t>235885</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>182717</t>
+          <t>183212</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>223829</t>
+          <t>223231</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>388586</t>
+          <t>383770</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>443433</t>
+          <t>442862</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>50,97%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>229151</t>
+          <t>228012</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>280103</t>
+          <t>279743</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>215211</t>
+          <t>215988</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>266143</t>
+          <t>264107</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>460555</t>
+          <t>459689</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>531318</t>
+          <t>526008</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,05%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>375543</t>
+          <t>375903</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>426495</t>
+          <t>427634</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>329010</t>
+          <t>331046</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>379942</t>
+          <t>379165</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>719481</t>
+          <t>724791</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>790244</t>
+          <t>791110</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,25%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>183814</t>
+          <t>183221</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>232680</t>
+          <t>231233</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>251390</t>
+          <t>253087</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>303296</t>
+          <t>304926</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>445887</t>
+          <t>450395</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>521232</t>
+          <t>522970</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,32%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>430812</t>
+          <t>432259</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>479678</t>
+          <t>480271</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>397784</t>
+          <t>396154</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>449690</t>
+          <t>447993</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>843340</t>
+          <t>841602</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>918685</t>
+          <t>914177</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>66,99%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>172874</t>
+          <t>171231</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>220932</t>
+          <t>220053</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>252820</t>
+          <t>255065</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>306779</t>
+          <t>309563</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>438990</t>
+          <t>440078</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>511016</t>
+          <t>513557</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>361938</t>
+          <t>362817</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>409996</t>
+          <t>411639</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>286334</t>
+          <t>283550</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>340293</t>
+          <t>338048</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>664967</t>
+          <t>662426</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>736993</t>
+          <t>735905</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,58%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>91921</t>
+          <t>92229</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>131394</t>
+          <t>129416</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>135522</t>
+          <t>135882</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>177042</t>
+          <t>176347</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>238603</t>
+          <t>237833</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>294971</t>
+          <t>298192</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,5%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>282021</t>
+          <t>283999</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>321494</t>
+          <t>321186</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>249572</t>
+          <t>250267</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>291092</t>
+          <t>290732</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>545058</t>
+          <t>541837</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>601426</t>
+          <t>602196</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,69%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39317</t>
+          <t>40363</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>65541</t>
+          <t>68481</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58703</t>
+          <t>58217</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87670</t>
+          <t>88606</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>104704</t>
+          <t>106315</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>146375</t>
+          <t>145416</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224849</t>
+          <t>221909</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>251073</t>
+          <t>250027</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>219129</t>
+          <t>218193</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>248096</t>
+          <t>248582</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>450815</t>
+          <t>451774</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>492486</t>
+          <t>490875</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,2%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15678</t>
+          <t>15188</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37592</t>
+          <t>36223</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43975</t>
+          <t>43735</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72800</t>
+          <t>72586</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65580</t>
+          <t>65100</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>100722</t>
+          <t>99531</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>189930</t>
+          <t>191299</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>211844</t>
+          <t>212334</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>245434</t>
+          <t>245648</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>274259</t>
+          <t>274499</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>445035</t>
+          <t>446226</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>480177</t>
+          <t>480657</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,07%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1027083</t>
+          <t>1019908</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1135492</t>
+          <t>1131297</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1240770</t>
+          <t>1243776</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1360887</t>
+          <t>1360681</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2297091</t>
+          <t>2296675</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2459735</t>
+          <t>2459791</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2144985</t>
+          <t>2149180</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2253394</t>
+          <t>2260569</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2001905</t>
+          <t>2002111</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2122022</t>
+          <t>2119016</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4183535</t>
+          <t>4183479</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4346179</t>
+          <t>4346595</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,43%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>144898</t>
+          <t>145544</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>185713</t>
+          <t>186290</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>121785</t>
+          <t>119851</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>157700</t>
+          <t>158420</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>278743</t>
+          <t>277384</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>330971</t>
+          <t>331725</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,84%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>225578</t>
+          <t>225001</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>266393</t>
+          <t>265747</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>223900</t>
+          <t>223180</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259815</t>
+          <t>261749</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>461920</t>
+          <t>461166</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>514148</t>
+          <t>515507</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>65,02%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>150638</t>
+          <t>149641</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>196024</t>
+          <t>194384</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>170534</t>
+          <t>169642</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>213086</t>
+          <t>212725</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>330252</t>
+          <t>334808</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>391399</t>
+          <t>398104</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>36,29%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>360675</t>
+          <t>362315</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>406061</t>
+          <t>407058</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327226</t>
+          <t>327587</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369778</t>
+          <t>370670</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>705612</t>
+          <t>698907</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>766759</t>
+          <t>762203</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,48%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>133001</t>
+          <t>131921</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>175293</t>
+          <t>179462</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>153985</t>
+          <t>151113</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>199460</t>
+          <t>195384</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>298745</t>
+          <t>298473</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>362669</t>
+          <t>359676</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>441899</t>
+          <t>437730</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>484191</t>
+          <t>485271</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>443746</t>
+          <t>447822</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>489221</t>
+          <t>492093</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>897729</t>
+          <t>900722</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>961653</t>
+          <t>961925</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,32%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>127560</t>
+          <t>123778</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>171803</t>
+          <t>169385</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>160048</t>
+          <t>159764</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>207138</t>
+          <t>206204</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>299602</t>
+          <t>296630</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>364210</t>
+          <t>363346</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,56%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>427061</t>
+          <t>429479</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>471304</t>
+          <t>475086</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>422992</t>
+          <t>423926</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>470082</t>
+          <t>470366</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>864784</t>
+          <t>865648</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>929392</t>
+          <t>932364</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,86%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86244</t>
+          <t>85991</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>123215</t>
+          <t>122926</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>96568</t>
+          <t>93967</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>134466</t>
+          <t>134439</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>191475</t>
+          <t>190440</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>244685</t>
+          <t>244776</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>319051</t>
+          <t>319340</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>356022</t>
+          <t>356275</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>319802</t>
+          <t>319829</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>357700</t>
+          <t>360301</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>651849</t>
+          <t>651758</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>705059</t>
+          <t>706094</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,76%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27576</t>
+          <t>27680</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51741</t>
+          <t>51102</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32833</t>
+          <t>31842</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58658</t>
+          <t>58212</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>66164</t>
+          <t>66754</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101210</t>
+          <t>102022</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253622</t>
+          <t>254261</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>277787</t>
+          <t>277683</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>263065</t>
+          <t>263511</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>288890</t>
+          <t>289881</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>525876</t>
+          <t>525064</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>560922</t>
+          <t>560332</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,35%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9649</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22055</t>
+          <t>22338</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21562</t>
+          <t>22216</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46321</t>
+          <t>46749</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>34626</t>
+          <t>34960</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>62721</t>
+          <t>62897</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>197212</t>
+          <t>196929</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>209618</t>
+          <t>209846</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>265776</t>
+          <t>265348</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>290535</t>
+          <t>289881</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>468644</t>
+          <t>468468</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>496739</t>
+          <t>496405</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,42%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>747042</t>
+          <t>747300</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>847666</t>
+          <t>845332</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>822229</t>
+          <t>828639</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>926247</t>
+          <t>927472</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1603052</t>
+          <t>1604204</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1748846</t>
+          <t>1744154</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2303276</t>
+          <t>2305610</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2403900</t>
+          <t>2403642</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2357090</t>
+          <t>2355865</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2461108</t>
+          <t>2454698</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4685433</t>
+          <t>4690125</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4831227</t>
+          <t>4830075</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,07%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>77905</t>
+          <t>76857</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50453</t>
+          <t>52919</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>109003</t>
+          <t>106309</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>65190</t>
+          <t>69866</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47859</t>
+          <t>51972</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>88189</t>
+          <t>93847</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>143095</t>
+          <t>146722</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>113458</t>
+          <t>114509</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>182169</t>
+          <t>184562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>24,86%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>312836</t>
+          <t>315185</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>281738</t>
+          <t>285733</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>340288</t>
+          <t>339123</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>237278</t>
+          <t>280378</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>214279</t>
+          <t>256397</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>254609</t>
+          <t>298272</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>550113</t>
+          <t>595564</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>511039</t>
+          <t>557724</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>579750</t>
+          <t>627777</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>84,57%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>390741</t>
+          <t>392042</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>390741</t>
+          <t>392042</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>390741</t>
+          <t>392042</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>302468</t>
+          <t>350244</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>302468</t>
+          <t>350244</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>302468</t>
+          <t>350244</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>693208</t>
+          <t>742286</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>693208</t>
+          <t>742286</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>693208</t>
+          <t>742286</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,22 +10008,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>64579</t>
+          <t>74490</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46712</t>
+          <t>52555</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87200</t>
+          <t>97417</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>82778</t>
+          <t>82369</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49739</t>
+          <t>66060</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105934</t>
+          <t>100252</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>147357</t>
+          <t>156859</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>112182</t>
+          <t>131767</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>180999</t>
+          <t>186332</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -10121,27 +10121,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>323661</t>
+          <t>362259</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>301040</t>
+          <t>339332</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>341528</t>
+          <t>384194</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>414503</t>
+          <t>400752</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>391347</t>
+          <t>382869</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>447542</t>
+          <t>417061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>738165</t>
+          <t>763011</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>704523</t>
+          <t>733538</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>773340</t>
+          <t>788103</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>85,68%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>388240</t>
+          <t>436749</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>388240</t>
+          <t>436749</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>388240</t>
+          <t>436749</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>497281</t>
+          <t>483121</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>497281</t>
+          <t>483121</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>497281</t>
+          <t>483121</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>885522</t>
+          <t>919870</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>885522</t>
+          <t>919870</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>885522</t>
+          <t>919870</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>45438</t>
+          <t>48816</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32749</t>
+          <t>37216</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60457</t>
+          <t>65842</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>73837</t>
+          <t>84154</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60900</t>
+          <t>69591</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86698</t>
+          <t>98157</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>119275</t>
+          <t>132970</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100145</t>
+          <t>113900</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>137776</t>
+          <t>156785</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>453321</t>
+          <t>523480</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>438302</t>
+          <t>506454</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>466010</t>
+          <t>535080</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>450376</t>
+          <t>518227</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>437515</t>
+          <t>504224</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>463313</t>
+          <t>532790</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>903697</t>
+          <t>1041708</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>885196</t>
+          <t>1017893</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>922827</t>
+          <t>1060778</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,3%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>498759</t>
+          <t>572296</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>498759</t>
+          <t>572296</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>498759</t>
+          <t>572296</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>524213</t>
+          <t>602381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>524213</t>
+          <t>602381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>524213</t>
+          <t>602381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1022972</t>
+          <t>1174678</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1022972</t>
+          <t>1174678</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1022972</t>
+          <t>1174678</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>308113</t>
+          <t>70100</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83337</t>
+          <t>55771</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>587150</t>
+          <t>88269</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>95106</t>
+          <t>103377</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79294</t>
+          <t>88208</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>110513</t>
+          <t>118345</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>403219</t>
+          <t>173477</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>180574</t>
+          <t>152332</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>895151</t>
+          <t>194585</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>505746</t>
+          <t>549680</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>226709</t>
+          <t>531511</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>730522</t>
+          <t>564009</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>597142</t>
+          <t>612605</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>581735</t>
+          <t>597637</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>612954</t>
+          <t>627774</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1102888</t>
+          <t>1162286</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>610956</t>
+          <t>1141178</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1325533</t>
+          <t>1183431</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,6%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>813859</t>
+          <t>619780</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>813859</t>
+          <t>619780</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>813859</t>
+          <t>619780</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>692248</t>
+          <t>715982</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>692248</t>
+          <t>715982</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>692248</t>
+          <t>715982</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1506107</t>
+          <t>1335763</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1506107</t>
+          <t>1335763</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1506107</t>
+          <t>1335763</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>64881</t>
+          <t>68076</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51878</t>
+          <t>52486</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>79525</t>
+          <t>82610</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>64967</t>
+          <t>70475</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54117</t>
+          <t>59392</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77173</t>
+          <t>83145</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>129848</t>
+          <t>138550</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113375</t>
+          <t>122083</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>148745</t>
+          <t>159078</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>446081</t>
+          <t>484235</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>431437</t>
+          <t>469701</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>459084</t>
+          <t>499825</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>427305</t>
+          <t>477670</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>415099</t>
+          <t>465000</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>438155</t>
+          <t>488753</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>873386</t>
+          <t>961905</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>854489</t>
+          <t>941377</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>889859</t>
+          <t>978372</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,91%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>510962</t>
+          <t>552311</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>510962</t>
+          <t>552311</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>510962</t>
+          <t>552311</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>492272</t>
+          <t>548145</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>492272</t>
+          <t>548145</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>492272</t>
+          <t>548145</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1003234</t>
+          <t>1100455</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1003234</t>
+          <t>1100455</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1003234</t>
+          <t>1100455</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>24285</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15675</t>
+          <t>17206</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30556</t>
+          <t>33345</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>32728</t>
+          <t>36151</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11694</t>
+          <t>27999</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57812</t>
+          <t>45639</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>54769</t>
+          <t>60437</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27679</t>
+          <t>48847</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76532</t>
+          <t>72331</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>304909</t>
+          <t>337608</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>296394</t>
+          <t>328548</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>311275</t>
+          <t>344687</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>507809</t>
+          <t>329324</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>482725</t>
+          <t>319836</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>528843</t>
+          <t>337476</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>812719</t>
+          <t>666931</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>790956</t>
+          <t>655037</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>839809</t>
+          <t>678521</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>93,28%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>326950</t>
+          <t>361893</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>326950</t>
+          <t>361893</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>326950</t>
+          <t>361893</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>540537</t>
+          <t>365475</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>540537</t>
+          <t>365475</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>540537</t>
+          <t>365475</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>867488</t>
+          <t>727368</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>867488</t>
+          <t>727368</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>867488</t>
+          <t>727368</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,22 +11723,22 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3764</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>8051</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>18786</t>
+          <t>21188</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13271</t>
+          <t>15214</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26125</t>
+          <t>29814</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>22089</t>
+          <t>24952</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15663</t>
+          <t>18456</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29385</t>
+          <t>34085</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -11836,27 +11836,27 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>237167</t>
+          <t>260337</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>233007</t>
+          <t>256050</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>239261</t>
+          <t>262793</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>296992</t>
+          <t>322765</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>289653</t>
+          <t>314139</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>302507</t>
+          <t>328739</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>534159</t>
+          <t>583103</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>526863</t>
+          <t>573970</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>540585</t>
+          <t>589599</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>240470</t>
+          <t>264101</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>240470</t>
+          <t>264101</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>240470</t>
+          <t>264101</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>315778</t>
+          <t>343953</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>315778</t>
+          <t>343953</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>315778</t>
+          <t>343953</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>556248</t>
+          <t>608055</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>556248</t>
+          <t>608055</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>556248</t>
+          <t>608055</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>586260</t>
+          <t>366387</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>354939</t>
+          <t>326728</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1164886</t>
+          <t>413423</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>433391</t>
+          <t>467580</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>344940</t>
+          <t>429704</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>485998</t>
+          <t>505219</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1019650</t>
+          <t>833968</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>776418</t>
+          <t>778596</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1717584</t>
+          <t>892654</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2583721</t>
+          <t>2832785</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2005095</t>
+          <t>2785749</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2815042</t>
+          <t>2872444</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2931406</t>
+          <t>2941722</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2878799</t>
+          <t>2904083</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3019857</t>
+          <t>2979598</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5515128</t>
+          <t>5774506</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4817194</t>
+          <t>5715820</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5758360</t>
+          <t>5829878</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,22%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3169981</t>
+          <t>3199172</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3169981</t>
+          <t>3199172</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3169981</t>
+          <t>3199172</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3364797</t>
+          <t>3409302</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3364797</t>
+          <t>3409302</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3364797</t>
+          <t>3409302</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>6534778</t>
+          <t>6608474</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6534778</t>
+          <t>6608474</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6534778</t>
+          <t>6608474</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
